--- a/app/Imports/excel-importation/2025-db-import.xlsx
+++ b/app/Imports/excel-importation/2025-db-import.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Developpement\grace_back\app\Imports\excel-importation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Developpement 2025\grace_back_prod\app\Imports\excel-importation\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4350AEC-5258-4612-B9B3-A7B7C9E9DBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="346">
   <si>
     <t>user_id</t>
   </si>
@@ -1062,12 +1063,15 @@
   </si>
   <si>
     <t>nationality</t>
+  </si>
+  <si>
+    <t>adresse</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1137,7 +1141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1151,6 +1155,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1430,8 +1435,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7" bestFit="1" customWidth="1"/>
@@ -1453,9 +1458,10 @@
     <col min="22" max="22" width="25.7109375" customWidth="1"/>
     <col min="23" max="23" width="13.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,10 +1535,13 @@
         <v>22</v>
       </c>
       <c r="Y1" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="Z1" s="6" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>5</v>
       </c>
@@ -1603,11 +1612,12 @@
       <c r="X2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="7"/>
+      <c r="Z2">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>5</v>
       </c>
@@ -1678,11 +1688,12 @@
       <c r="X3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="7"/>
+      <c r="Z3">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>5</v>
       </c>
@@ -1749,11 +1760,12 @@
       <c r="X4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="7"/>
+      <c r="Z4">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>5</v>
       </c>
@@ -1824,11 +1836,12 @@
       <c r="X5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="7"/>
+      <c r="Z5">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1899,11 +1912,12 @@
       <c r="X6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="7"/>
+      <c r="Z6">
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -1974,11 +1988,12 @@
       <c r="X7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="7"/>
+      <c r="Z7">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -2049,11 +2064,12 @@
       <c r="X8" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="7"/>
+      <c r="Z8">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -2124,11 +2140,12 @@
       <c r="X9" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="7"/>
+      <c r="Z9">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -2199,8 +2216,9 @@
       <c r="X10" s="3" t="s">
         <v>134</v>
       </c>
+      <c r="Y10" s="7"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -2271,8 +2289,9 @@
       <c r="X11" s="3" t="s">
         <v>147</v>
       </c>
+      <c r="Y11" s="7"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -2343,8 +2362,9 @@
       <c r="X12" s="3" t="s">
         <v>159</v>
       </c>
+      <c r="Y12" s="7"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>5</v>
       </c>
@@ -2415,8 +2435,9 @@
       <c r="X13" s="3" t="s">
         <v>172</v>
       </c>
+      <c r="Y13" s="7"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>5</v>
       </c>
@@ -2485,8 +2506,9 @@
       <c r="X14" s="3" t="s">
         <v>184</v>
       </c>
+      <c r="Y14" s="7"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -2555,11 +2577,12 @@
       <c r="X15" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="7"/>
+      <c r="Z15">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>5</v>
       </c>
@@ -2628,11 +2651,12 @@
       <c r="X16" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="7"/>
+      <c r="Z16">
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>5</v>
       </c>
@@ -2701,11 +2725,12 @@
       <c r="X17" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="7"/>
+      <c r="Z17">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -2774,11 +2799,12 @@
       <c r="X18" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="7"/>
+      <c r="Z18">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>5</v>
       </c>
@@ -2847,11 +2873,12 @@
       <c r="X19" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="7"/>
+      <c r="Z19">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>5</v>
       </c>
@@ -2922,11 +2949,12 @@
       <c r="X20" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="7"/>
+      <c r="Z20">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>5</v>
       </c>
@@ -2997,11 +3025,12 @@
       <c r="X21" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="7"/>
+      <c r="Z21">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>5</v>
       </c>
@@ -3072,11 +3101,12 @@
       <c r="X22" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="7"/>
+      <c r="Z22">
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>5</v>
       </c>
@@ -3147,11 +3177,12 @@
       <c r="X23" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="7"/>
+      <c r="Z23">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>5</v>
       </c>
@@ -3222,11 +3253,12 @@
       <c r="X24" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="7"/>
+      <c r="Z24">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>5</v>
       </c>
@@ -3293,11 +3325,12 @@
       <c r="X25" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="7"/>
+      <c r="Z25">
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>5</v>
       </c>
@@ -3364,11 +3397,12 @@
       <c r="X26" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="7"/>
+      <c r="Z26">
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>5</v>
       </c>
@@ -3435,11 +3469,12 @@
       <c r="X27" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="7"/>
+      <c r="Z27">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>5</v>
       </c>
@@ -3506,12 +3541,13 @@
       <c r="X28" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="7"/>
+      <c r="Z28">
         <v>99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:X28"/>
+  <autoFilter ref="B1:X28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
